--- a/Data/ECON_소비자동향조사(전국, 월, 2008.9~)_KK.xlsx
+++ b/Data/ECON_소비자동향조사(전국, 월, 2008.9~)_KK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\내 드라이브\Research\SavedData\KorailEconNews\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DataScience\Lecture\특강_20250412_한국지능정보사회진흥원_빅데이터센터\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D827702-DF0B-413D-855F-70011E37D84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53F898A-808F-49A4-8576-0F94D3799E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24098" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="데이터" sheetId="1" r:id="rId1"/>
@@ -629,7 +629,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.0_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -639,11 +639,15 @@
       <sz val="10.5"/>
       <color rgb="FF555555"/>
       <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF888282"/>
       <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="8"/>
@@ -719,10 +723,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1060,572 +1064,572 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CK131"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22"/>
     <col min="2" max="89" width="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:89" ht="23.25" customHeight="1">
+    <row r="1" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5"/>
-      <c r="AK1" s="5"/>
-      <c r="AL1" s="5"/>
-      <c r="AM1" s="5"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="5"/>
-      <c r="AS1" s="5"/>
-      <c r="AT1" s="5"/>
-      <c r="AU1" s="5"/>
-      <c r="AV1" s="5"/>
-      <c r="AW1" s="5"/>
-      <c r="AX1" s="5"/>
-      <c r="AY1" s="5"/>
-      <c r="AZ1" s="5"/>
-      <c r="BA1" s="5"/>
-      <c r="BB1" s="5"/>
-      <c r="BC1" s="5"/>
-      <c r="BD1" s="5"/>
-      <c r="BE1" s="5"/>
-      <c r="BF1" s="5"/>
-      <c r="BG1" s="5"/>
-      <c r="BH1" s="5"/>
-      <c r="BI1" s="5"/>
-      <c r="BJ1" s="5"/>
-      <c r="BK1" s="5"/>
-      <c r="BL1" s="5"/>
-      <c r="BM1" s="5"/>
-      <c r="BN1" s="5"/>
-      <c r="BO1" s="5"/>
-      <c r="BP1" s="5"/>
-      <c r="BQ1" s="5"/>
-      <c r="BR1" s="5"/>
-      <c r="BS1" s="5"/>
-      <c r="BT1" s="5"/>
-      <c r="BU1" s="5"/>
-      <c r="BV1" s="5"/>
-      <c r="BW1" s="5"/>
-      <c r="BX1" s="5"/>
-      <c r="BY1" s="5"/>
-      <c r="BZ1" s="5"/>
-      <c r="CA1" s="5"/>
-      <c r="CB1" s="5"/>
-      <c r="CC1" s="5"/>
-      <c r="CD1" s="5"/>
-      <c r="CE1" s="5"/>
-      <c r="CF1" s="5"/>
-      <c r="CG1" s="5"/>
-      <c r="CH1" s="5"/>
-      <c r="CI1" s="5"/>
-      <c r="CJ1" s="5"/>
-      <c r="CK1" s="5"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
+      <c r="AP1" s="6"/>
+      <c r="AQ1" s="6"/>
+      <c r="AR1" s="6"/>
+      <c r="AS1" s="6"/>
+      <c r="AT1" s="6"/>
+      <c r="AU1" s="6"/>
+      <c r="AV1" s="6"/>
+      <c r="AW1" s="6"/>
+      <c r="AX1" s="6"/>
+      <c r="AY1" s="6"/>
+      <c r="AZ1" s="6"/>
+      <c r="BA1" s="6"/>
+      <c r="BB1" s="6"/>
+      <c r="BC1" s="6"/>
+      <c r="BD1" s="6"/>
+      <c r="BE1" s="6"/>
+      <c r="BF1" s="6"/>
+      <c r="BG1" s="6"/>
+      <c r="BH1" s="6"/>
+      <c r="BI1" s="6"/>
+      <c r="BJ1" s="6"/>
+      <c r="BK1" s="6"/>
+      <c r="BL1" s="6"/>
+      <c r="BM1" s="6"/>
+      <c r="BN1" s="6"/>
+      <c r="BO1" s="6"/>
+      <c r="BP1" s="6"/>
+      <c r="BQ1" s="6"/>
+      <c r="BR1" s="6"/>
+      <c r="BS1" s="6"/>
+      <c r="BT1" s="6"/>
+      <c r="BU1" s="6"/>
+      <c r="BV1" s="6"/>
+      <c r="BW1" s="6"/>
+      <c r="BX1" s="6"/>
+      <c r="BY1" s="6"/>
+      <c r="BZ1" s="6"/>
+      <c r="CA1" s="6"/>
+      <c r="CB1" s="6"/>
+      <c r="CC1" s="6"/>
+      <c r="CD1" s="6"/>
+      <c r="CE1" s="6"/>
+      <c r="CF1" s="6"/>
+      <c r="CG1" s="6"/>
+      <c r="CH1" s="6"/>
+      <c r="CI1" s="6"/>
+      <c r="CJ1" s="6"/>
+      <c r="CK1" s="6"/>
     </row>
-    <row r="2" spans="1:89" ht="23.25" customHeight="1">
+    <row r="2" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="5"/>
-      <c r="BC2" s="5"/>
-      <c r="BD2" s="5"/>
-      <c r="BE2" s="5"/>
-      <c r="BF2" s="5"/>
-      <c r="BG2" s="5"/>
-      <c r="BH2" s="5"/>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="5"/>
-      <c r="BK2" s="5"/>
-      <c r="BL2" s="5"/>
-      <c r="BM2" s="5"/>
-      <c r="BN2" s="5"/>
-      <c r="BO2" s="5"/>
-      <c r="BP2" s="5"/>
-      <c r="BQ2" s="5"/>
-      <c r="BR2" s="5"/>
-      <c r="BS2" s="5"/>
-      <c r="BT2" s="5"/>
-      <c r="BU2" s="5"/>
-      <c r="BV2" s="5"/>
-      <c r="BW2" s="5"/>
-      <c r="BX2" s="5"/>
-      <c r="BY2" s="5"/>
-      <c r="BZ2" s="5"/>
-      <c r="CA2" s="5"/>
-      <c r="CB2" s="5"/>
-      <c r="CC2" s="5"/>
-      <c r="CD2" s="5"/>
-      <c r="CE2" s="5"/>
-      <c r="CF2" s="5"/>
-      <c r="CG2" s="5"/>
-      <c r="CH2" s="5"/>
-      <c r="CI2" s="5"/>
-      <c r="CJ2" s="5"/>
-      <c r="CK2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+      <c r="AP2" s="6"/>
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="6"/>
+      <c r="AT2" s="6"/>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="6"/>
+      <c r="AX2" s="6"/>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="6"/>
+      <c r="BA2" s="6"/>
+      <c r="BB2" s="6"/>
+      <c r="BC2" s="6"/>
+      <c r="BD2" s="6"/>
+      <c r="BE2" s="6"/>
+      <c r="BF2" s="6"/>
+      <c r="BG2" s="6"/>
+      <c r="BH2" s="6"/>
+      <c r="BI2" s="6"/>
+      <c r="BJ2" s="6"/>
+      <c r="BK2" s="6"/>
+      <c r="BL2" s="6"/>
+      <c r="BM2" s="6"/>
+      <c r="BN2" s="6"/>
+      <c r="BO2" s="6"/>
+      <c r="BP2" s="6"/>
+      <c r="BQ2" s="6"/>
+      <c r="BR2" s="6"/>
+      <c r="BS2" s="6"/>
+      <c r="BT2" s="6"/>
+      <c r="BU2" s="6"/>
+      <c r="BV2" s="6"/>
+      <c r="BW2" s="6"/>
+      <c r="BX2" s="6"/>
+      <c r="BY2" s="6"/>
+      <c r="BZ2" s="6"/>
+      <c r="CA2" s="6"/>
+      <c r="CB2" s="6"/>
+      <c r="CC2" s="6"/>
+      <c r="CD2" s="6"/>
+      <c r="CE2" s="6"/>
+      <c r="CF2" s="6"/>
+      <c r="CG2" s="6"/>
+      <c r="CH2" s="6"/>
+      <c r="CI2" s="6"/>
+      <c r="CJ2" s="6"/>
+      <c r="CK2" s="6"/>
     </row>
-    <row r="3" spans="1:89" ht="23.25" customHeight="1">
+    <row r="3" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="5"/>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="5"/>
-      <c r="AJ3" s="5"/>
-      <c r="AK3" s="5"/>
-      <c r="AL3" s="5"/>
-      <c r="AM3" s="5"/>
-      <c r="AN3" s="5"/>
-      <c r="AO3" s="5"/>
-      <c r="AP3" s="5"/>
-      <c r="AQ3" s="5"/>
-      <c r="AR3" s="5"/>
-      <c r="AS3" s="5"/>
-      <c r="AT3" s="5"/>
-      <c r="AU3" s="5"/>
-      <c r="AV3" s="5"/>
-      <c r="AW3" s="5"/>
-      <c r="AX3" s="5"/>
-      <c r="AY3" s="5"/>
-      <c r="AZ3" s="5"/>
-      <c r="BA3" s="5"/>
-      <c r="BB3" s="5"/>
-      <c r="BC3" s="5"/>
-      <c r="BD3" s="5"/>
-      <c r="BE3" s="5"/>
-      <c r="BF3" s="5"/>
-      <c r="BG3" s="5"/>
-      <c r="BH3" s="5"/>
-      <c r="BI3" s="5"/>
-      <c r="BJ3" s="5"/>
-      <c r="BK3" s="5"/>
-      <c r="BL3" s="5"/>
-      <c r="BM3" s="5"/>
-      <c r="BN3" s="5"/>
-      <c r="BO3" s="5"/>
-      <c r="BP3" s="5"/>
-      <c r="BQ3" s="5"/>
-      <c r="BR3" s="5"/>
-      <c r="BS3" s="5"/>
-      <c r="BT3" s="5"/>
-      <c r="BU3" s="5"/>
-      <c r="BV3" s="5"/>
-      <c r="BW3" s="5"/>
-      <c r="BX3" s="5"/>
-      <c r="BY3" s="5"/>
-      <c r="BZ3" s="5"/>
-      <c r="CA3" s="5"/>
-      <c r="CB3" s="5"/>
-      <c r="CC3" s="5"/>
-      <c r="CD3" s="5"/>
-      <c r="CE3" s="5"/>
-      <c r="CF3" s="5"/>
-      <c r="CG3" s="5"/>
-      <c r="CH3" s="5"/>
-      <c r="CI3" s="5"/>
-      <c r="CJ3" s="5"/>
-      <c r="CK3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="6"/>
+      <c r="AJ3" s="6"/>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="6"/>
+      <c r="AM3" s="6"/>
+      <c r="AN3" s="6"/>
+      <c r="AO3" s="6"/>
+      <c r="AP3" s="6"/>
+      <c r="AQ3" s="6"/>
+      <c r="AR3" s="6"/>
+      <c r="AS3" s="6"/>
+      <c r="AT3" s="6"/>
+      <c r="AU3" s="6"/>
+      <c r="AV3" s="6"/>
+      <c r="AW3" s="6"/>
+      <c r="AX3" s="6"/>
+      <c r="AY3" s="6"/>
+      <c r="AZ3" s="6"/>
+      <c r="BA3" s="6"/>
+      <c r="BB3" s="6"/>
+      <c r="BC3" s="6"/>
+      <c r="BD3" s="6"/>
+      <c r="BE3" s="6"/>
+      <c r="BF3" s="6"/>
+      <c r="BG3" s="6"/>
+      <c r="BH3" s="6"/>
+      <c r="BI3" s="6"/>
+      <c r="BJ3" s="6"/>
+      <c r="BK3" s="6"/>
+      <c r="BL3" s="6"/>
+      <c r="BM3" s="6"/>
+      <c r="BN3" s="6"/>
+      <c r="BO3" s="6"/>
+      <c r="BP3" s="6"/>
+      <c r="BQ3" s="6"/>
+      <c r="BR3" s="6"/>
+      <c r="BS3" s="6"/>
+      <c r="BT3" s="6"/>
+      <c r="BU3" s="6"/>
+      <c r="BV3" s="6"/>
+      <c r="BW3" s="6"/>
+      <c r="BX3" s="6"/>
+      <c r="BY3" s="6"/>
+      <c r="BZ3" s="6"/>
+      <c r="CA3" s="6"/>
+      <c r="CB3" s="6"/>
+      <c r="CC3" s="6"/>
+      <c r="CD3" s="6"/>
+      <c r="CE3" s="6"/>
+      <c r="CF3" s="6"/>
+      <c r="CG3" s="6"/>
+      <c r="CH3" s="6"/>
+      <c r="CI3" s="6"/>
+      <c r="CJ3" s="6"/>
+      <c r="CK3" s="6"/>
     </row>
-    <row r="4" spans="1:89" ht="23.25" customHeight="1">
+    <row r="4" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5" t="s">
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5" t="s">
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5" t="s">
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5" t="s">
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5" t="s">
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5" t="s">
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
-      <c r="AK4" s="5"/>
-      <c r="AL4" s="5" t="s">
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="6"/>
+      <c r="AL4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AM4" s="5"/>
-      <c r="AN4" s="5"/>
-      <c r="AO4" s="5"/>
-      <c r="AP4" s="5" t="s">
+      <c r="AM4" s="6"/>
+      <c r="AN4" s="6"/>
+      <c r="AO4" s="6"/>
+      <c r="AP4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AQ4" s="5"/>
-      <c r="AR4" s="5"/>
-      <c r="AS4" s="5"/>
-      <c r="AT4" s="5" t="s">
+      <c r="AQ4" s="6"/>
+      <c r="AR4" s="6"/>
+      <c r="AS4" s="6"/>
+      <c r="AT4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AU4" s="5"/>
-      <c r="AV4" s="5"/>
-      <c r="AW4" s="5"/>
-      <c r="AX4" s="5" t="s">
+      <c r="AU4" s="6"/>
+      <c r="AV4" s="6"/>
+      <c r="AW4" s="6"/>
+      <c r="AX4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AY4" s="5"/>
-      <c r="AZ4" s="5"/>
-      <c r="BA4" s="5"/>
-      <c r="BB4" s="5" t="s">
+      <c r="AY4" s="6"/>
+      <c r="AZ4" s="6"/>
+      <c r="BA4" s="6"/>
+      <c r="BB4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="BC4" s="5"/>
-      <c r="BD4" s="5"/>
-      <c r="BE4" s="5"/>
-      <c r="BF4" s="5" t="s">
+      <c r="BC4" s="6"/>
+      <c r="BD4" s="6"/>
+      <c r="BE4" s="6"/>
+      <c r="BF4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="BG4" s="5"/>
-      <c r="BH4" s="5"/>
-      <c r="BI4" s="5"/>
-      <c r="BJ4" s="5" t="s">
+      <c r="BG4" s="6"/>
+      <c r="BH4" s="6"/>
+      <c r="BI4" s="6"/>
+      <c r="BJ4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="BK4" s="5"/>
-      <c r="BL4" s="5"/>
-      <c r="BM4" s="5"/>
-      <c r="BN4" s="5" t="s">
+      <c r="BK4" s="6"/>
+      <c r="BL4" s="6"/>
+      <c r="BM4" s="6"/>
+      <c r="BN4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="BO4" s="5"/>
-      <c r="BP4" s="5"/>
-      <c r="BQ4" s="5"/>
-      <c r="BR4" s="5" t="s">
+      <c r="BO4" s="6"/>
+      <c r="BP4" s="6"/>
+      <c r="BQ4" s="6"/>
+      <c r="BR4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="BS4" s="5"/>
-      <c r="BT4" s="5"/>
-      <c r="BU4" s="5"/>
-      <c r="BV4" s="5" t="s">
+      <c r="BS4" s="6"/>
+      <c r="BT4" s="6"/>
+      <c r="BU4" s="6"/>
+      <c r="BV4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="BW4" s="5"/>
-      <c r="BX4" s="5"/>
-      <c r="BY4" s="5"/>
-      <c r="BZ4" s="5" t="s">
+      <c r="BW4" s="6"/>
+      <c r="BX4" s="6"/>
+      <c r="BY4" s="6"/>
+      <c r="BZ4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="CA4" s="5"/>
-      <c r="CB4" s="5"/>
-      <c r="CC4" s="5"/>
-      <c r="CD4" s="5" t="s">
+      <c r="CA4" s="6"/>
+      <c r="CB4" s="6"/>
+      <c r="CC4" s="6"/>
+      <c r="CD4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="CE4" s="5"/>
-      <c r="CF4" s="5"/>
-      <c r="CG4" s="5"/>
-      <c r="CH4" s="5" t="s">
+      <c r="CE4" s="6"/>
+      <c r="CF4" s="6"/>
+      <c r="CG4" s="6"/>
+      <c r="CH4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="CI4" s="5"/>
-      <c r="CJ4" s="5"/>
-      <c r="CK4" s="5"/>
+      <c r="CI4" s="6"/>
+      <c r="CJ4" s="6"/>
+      <c r="CK4" s="6"/>
     </row>
-    <row r="5" spans="1:89" ht="23.25" customHeight="1">
+    <row r="5" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5" t="s">
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5" t="s">
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5" t="s">
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5" t="s">
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="5"/>
-      <c r="AD5" s="5" t="s">
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="6"/>
+      <c r="AD5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AE5" s="5"/>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="5"/>
-      <c r="AH5" s="5" t="s">
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6"/>
+      <c r="AG5" s="6"/>
+      <c r="AH5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AI5" s="5"/>
-      <c r="AJ5" s="5"/>
-      <c r="AK5" s="5"/>
-      <c r="AL5" s="5" t="s">
+      <c r="AI5" s="6"/>
+      <c r="AJ5" s="6"/>
+      <c r="AK5" s="6"/>
+      <c r="AL5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AM5" s="5"/>
-      <c r="AN5" s="5"/>
-      <c r="AO5" s="5"/>
-      <c r="AP5" s="5" t="s">
+      <c r="AM5" s="6"/>
+      <c r="AN5" s="6"/>
+      <c r="AO5" s="6"/>
+      <c r="AP5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AQ5" s="5"/>
-      <c r="AR5" s="5"/>
-      <c r="AS5" s="5"/>
-      <c r="AT5" s="5" t="s">
+      <c r="AQ5" s="6"/>
+      <c r="AR5" s="6"/>
+      <c r="AS5" s="6"/>
+      <c r="AT5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AU5" s="5"/>
-      <c r="AV5" s="5"/>
-      <c r="AW5" s="5"/>
-      <c r="AX5" s="5" t="s">
+      <c r="AU5" s="6"/>
+      <c r="AV5" s="6"/>
+      <c r="AW5" s="6"/>
+      <c r="AX5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AY5" s="5"/>
-      <c r="AZ5" s="5"/>
-      <c r="BA5" s="5"/>
-      <c r="BB5" s="5" t="s">
+      <c r="AY5" s="6"/>
+      <c r="AZ5" s="6"/>
+      <c r="BA5" s="6"/>
+      <c r="BB5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BC5" s="5"/>
-      <c r="BD5" s="5"/>
-      <c r="BE5" s="5"/>
-      <c r="BF5" s="5" t="s">
+      <c r="BC5" s="6"/>
+      <c r="BD5" s="6"/>
+      <c r="BE5" s="6"/>
+      <c r="BF5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BG5" s="5"/>
-      <c r="BH5" s="5"/>
-      <c r="BI5" s="5"/>
-      <c r="BJ5" s="5" t="s">
+      <c r="BG5" s="6"/>
+      <c r="BH5" s="6"/>
+      <c r="BI5" s="6"/>
+      <c r="BJ5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="BK5" s="5"/>
-      <c r="BL5" s="5"/>
-      <c r="BM5" s="5"/>
-      <c r="BN5" s="5" t="s">
+      <c r="BK5" s="6"/>
+      <c r="BL5" s="6"/>
+      <c r="BM5" s="6"/>
+      <c r="BN5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BO5" s="5"/>
-      <c r="BP5" s="5"/>
-      <c r="BQ5" s="5"/>
-      <c r="BR5" s="5" t="s">
+      <c r="BO5" s="6"/>
+      <c r="BP5" s="6"/>
+      <c r="BQ5" s="6"/>
+      <c r="BR5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BS5" s="5"/>
-      <c r="BT5" s="5"/>
-      <c r="BU5" s="5"/>
-      <c r="BV5" s="5" t="s">
+      <c r="BS5" s="6"/>
+      <c r="BT5" s="6"/>
+      <c r="BU5" s="6"/>
+      <c r="BV5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="BW5" s="5"/>
-      <c r="BX5" s="5"/>
-      <c r="BY5" s="5"/>
-      <c r="BZ5" s="5" t="s">
+      <c r="BW5" s="6"/>
+      <c r="BX5" s="6"/>
+      <c r="BY5" s="6"/>
+      <c r="BZ5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="CA5" s="5"/>
-      <c r="CB5" s="5"/>
-      <c r="CC5" s="5"/>
-      <c r="CD5" s="5" t="s">
+      <c r="CA5" s="6"/>
+      <c r="CB5" s="6"/>
+      <c r="CC5" s="6"/>
+      <c r="CD5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="CE5" s="5"/>
-      <c r="CF5" s="5"/>
-      <c r="CG5" s="5"/>
-      <c r="CH5" s="5" t="s">
+      <c r="CE5" s="6"/>
+      <c r="CF5" s="6"/>
+      <c r="CG5" s="6"/>
+      <c r="CH5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="CI5" s="5"/>
-      <c r="CJ5" s="5"/>
-      <c r="CK5" s="5"/>
+      <c r="CI5" s="6"/>
+      <c r="CJ5" s="6"/>
+      <c r="CK5" s="6"/>
     </row>
-    <row r="6" spans="1:89" ht="23.25" customHeight="1">
+    <row r="6" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>52</v>
       </c>
@@ -1894,7 +1898,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:89" ht="23.25" customHeight="1">
+    <row r="7" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>54</v>
       </c>
@@ -2163,108 +2167,108 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:89" ht="23.25" customHeight="1">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B8" s="6" t="str">
+      <c r="B8" s="5" t="str">
         <f>$B$3&amp;"_"&amp;B7</f>
         <v>소비자심리지수_원자료</v>
       </c>
-      <c r="C8" s="6" t="str">
+      <c r="C8" s="5" t="str">
         <f t="shared" ref="C8:E8" si="0">$B$3&amp;"_"&amp;C7</f>
         <v>소비자심리지수_전기대비증감</v>
       </c>
-      <c r="D8" s="6" t="str">
+      <c r="D8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>소비자심리지수_전년동기대비증감</v>
       </c>
-      <c r="E8" s="6" t="str">
+      <c r="E8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>소비자심리지수_이동평균(3기간)</v>
       </c>
-      <c r="F8" s="6" t="str">
+      <c r="F8" s="5" t="str">
         <f>$F$3&amp;"_"&amp;F7</f>
         <v>_원자료</v>
       </c>
-      <c r="G8" s="6" t="str">
+      <c r="G8" s="5" t="str">
         <f t="shared" ref="G8:I8" si="1">$F$3&amp;"_"&amp;G7</f>
         <v>_전기대비증감</v>
       </c>
-      <c r="H8" s="6" t="str">
+      <c r="H8" s="5" t="str">
         <f t="shared" si="1"/>
         <v>_전년동기대비증감</v>
       </c>
-      <c r="I8" s="6" t="str">
+      <c r="I8" s="5" t="str">
         <f t="shared" si="1"/>
         <v>_이동평균(3기간)</v>
       </c>
-      <c r="J8" s="6" t="str">
+      <c r="J8" s="5" t="str">
         <f>$J$3&amp;"_"&amp;J7</f>
         <v>_원자료</v>
       </c>
-      <c r="K8" s="6" t="str">
+      <c r="K8" s="5" t="str">
         <f t="shared" ref="K8:M8" si="2">$J$3&amp;"_"&amp;K7</f>
         <v>_전기대비증감</v>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="5" t="str">
         <f t="shared" si="2"/>
         <v>_전년동기대비증감</v>
       </c>
-      <c r="M8" s="6" t="str">
+      <c r="M8" s="5" t="str">
         <f t="shared" si="2"/>
         <v>_이동평균(3기간)</v>
       </c>
-      <c r="N8" s="6" t="str">
+      <c r="N8" s="5" t="str">
         <f>$N$3&amp;"_"&amp;N7</f>
         <v>_원자료</v>
       </c>
-      <c r="O8" s="6" t="str">
+      <c r="O8" s="5" t="str">
         <f t="shared" ref="O8:Q8" si="3">$N$3&amp;"_"&amp;O7</f>
         <v>_전기대비증감</v>
       </c>
-      <c r="P8" s="6" t="str">
+      <c r="P8" s="5" t="str">
         <f t="shared" si="3"/>
         <v>_전년동기대비증감</v>
       </c>
-      <c r="Q8" s="6" t="str">
+      <c r="Q8" s="5" t="str">
         <f t="shared" si="3"/>
         <v>_이동평균(3기간)</v>
       </c>
-      <c r="R8" s="6" t="str">
+      <c r="R8" s="5" t="str">
         <f>$R$3&amp;"_"&amp;R7</f>
         <v>_원자료</v>
       </c>
-      <c r="S8" s="6" t="str">
+      <c r="S8" s="5" t="str">
         <f t="shared" ref="S8:U8" si="4">$R$3&amp;"_"&amp;S7</f>
         <v>_전기대비증감</v>
       </c>
-      <c r="T8" s="6" t="str">
+      <c r="T8" s="5" t="str">
         <f t="shared" si="4"/>
         <v>_전년동기대비증감</v>
       </c>
-      <c r="U8" s="6" t="str">
+      <c r="U8" s="5" t="str">
         <f t="shared" si="4"/>
         <v>_이동평균(3기간)</v>
       </c>
-      <c r="V8" s="6" t="str">
+      <c r="V8" s="5" t="str">
         <f>$V$3&amp;"_"&amp;V7</f>
         <v>_원자료</v>
       </c>
-      <c r="W8" s="6" t="str">
+      <c r="W8" s="5" t="str">
         <f t="shared" ref="W8:Y8" si="5">$V$3&amp;"_"&amp;W7</f>
         <v>_전기대비증감</v>
       </c>
-      <c r="X8" s="6" t="str">
+      <c r="X8" s="5" t="str">
         <f t="shared" si="5"/>
         <v>_전년동기대비증감</v>
       </c>
-      <c r="Y8" s="6" t="str">
+      <c r="Y8" s="5" t="str">
         <f t="shared" si="5"/>
         <v>_이동평균(3기간)</v>
       </c>
     </row>
-    <row r="9" spans="1:89" ht="23.25" customHeight="1">
+    <row r="9" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>59</v>
       </c>
@@ -2365,7 +2369,7 @@
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
     </row>
-    <row r="10" spans="1:89" ht="23.25" customHeight="1">
+    <row r="10" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -2466,7 +2470,7 @@
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
     </row>
-    <row r="11" spans="1:89" ht="23.25" customHeight="1">
+    <row r="11" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>61</v>
       </c>
@@ -2567,7 +2571,7 @@
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
     </row>
-    <row r="12" spans="1:89" ht="23.25" customHeight="1">
+    <row r="12" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>62</v>
       </c>
@@ -2668,7 +2672,7 @@
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
     </row>
-    <row r="13" spans="1:89" ht="23.25" customHeight="1">
+    <row r="13" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>63</v>
       </c>
@@ -2769,7 +2773,7 @@
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
     </row>
-    <row r="14" spans="1:89" ht="23.25" customHeight="1">
+    <row r="14" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>64</v>
       </c>
@@ -2870,7 +2874,7 @@
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
     </row>
-    <row r="15" spans="1:89" ht="23.25" customHeight="1">
+    <row r="15" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>65</v>
       </c>
@@ -2971,7 +2975,7 @@
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
     </row>
-    <row r="16" spans="1:89" ht="23.25" customHeight="1">
+    <row r="16" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>66</v>
       </c>
@@ -3072,7 +3076,7 @@
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
     </row>
-    <row r="17" spans="1:89" ht="23.25" customHeight="1">
+    <row r="17" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>67</v>
       </c>
@@ -3173,7 +3177,7 @@
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
     </row>
-    <row r="18" spans="1:89" ht="23.25" customHeight="1">
+    <row r="18" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>68</v>
       </c>
@@ -3274,7 +3278,7 @@
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
     </row>
-    <row r="19" spans="1:89" ht="23.25" customHeight="1">
+    <row r="19" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>69</v>
       </c>
@@ -3375,7 +3379,7 @@
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
     </row>
-    <row r="20" spans="1:89" ht="23.25" customHeight="1">
+    <row r="20" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>70</v>
       </c>
@@ -3476,7 +3480,7 @@
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
     </row>
-    <row r="21" spans="1:89" ht="23.25" customHeight="1">
+    <row r="21" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>71</v>
       </c>
@@ -3577,7 +3581,7 @@
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
     </row>
-    <row r="22" spans="1:89" ht="23.25" customHeight="1">
+    <row r="22" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>72</v>
       </c>
@@ -3678,7 +3682,7 @@
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
     </row>
-    <row r="23" spans="1:89" ht="23.25" customHeight="1">
+    <row r="23" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>73</v>
       </c>
@@ -3779,7 +3783,7 @@
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
     </row>
-    <row r="24" spans="1:89" ht="23.25" customHeight="1">
+    <row r="24" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>74</v>
       </c>
@@ -3880,7 +3884,7 @@
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
     </row>
-    <row r="25" spans="1:89" ht="23.25" customHeight="1">
+    <row r="25" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>75</v>
       </c>
@@ -3981,7 +3985,7 @@
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
     </row>
-    <row r="26" spans="1:89" ht="23.25" customHeight="1">
+    <row r="26" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>76</v>
       </c>
@@ -4082,7 +4086,7 @@
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
     </row>
-    <row r="27" spans="1:89" ht="23.25" customHeight="1">
+    <row r="27" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>77</v>
       </c>
@@ -4183,7 +4187,7 @@
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
     </row>
-    <row r="28" spans="1:89" ht="23.25" customHeight="1">
+    <row r="28" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>78</v>
       </c>
@@ -4284,7 +4288,7 @@
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
     </row>
-    <row r="29" spans="1:89" ht="23.25" customHeight="1">
+    <row r="29" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>79</v>
       </c>
@@ -4385,7 +4389,7 @@
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
     </row>
-    <row r="30" spans="1:89" ht="23.25" customHeight="1">
+    <row r="30" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>80</v>
       </c>
@@ -4486,7 +4490,7 @@
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
     </row>
-    <row r="31" spans="1:89" ht="23.25" customHeight="1">
+    <row r="31" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>81</v>
       </c>
@@ -4587,7 +4591,7 @@
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
     </row>
-    <row r="32" spans="1:89" ht="23.25" customHeight="1">
+    <row r="32" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>82</v>
       </c>
@@ -4688,7 +4692,7 @@
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
     </row>
-    <row r="33" spans="1:89" ht="23.25" customHeight="1">
+    <row r="33" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>83</v>
       </c>
@@ -4789,7 +4793,7 @@
       <c r="CJ33" s="3"/>
       <c r="CK33" s="3"/>
     </row>
-    <row r="34" spans="1:89" ht="23.25" customHeight="1">
+    <row r="34" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>84</v>
       </c>
@@ -4890,7 +4894,7 @@
       <c r="CJ34" s="3"/>
       <c r="CK34" s="3"/>
     </row>
-    <row r="35" spans="1:89" ht="23.25" customHeight="1">
+    <row r="35" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>85</v>
       </c>
@@ -4991,7 +4995,7 @@
       <c r="CJ35" s="3"/>
       <c r="CK35" s="3"/>
     </row>
-    <row r="36" spans="1:89" ht="23.25" customHeight="1">
+    <row r="36" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>86</v>
       </c>
@@ -5092,7 +5096,7 @@
       <c r="CJ36" s="3"/>
       <c r="CK36" s="3"/>
     </row>
-    <row r="37" spans="1:89" ht="23.25" customHeight="1">
+    <row r="37" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>87</v>
       </c>
@@ -5193,7 +5197,7 @@
       <c r="CJ37" s="3"/>
       <c r="CK37" s="3"/>
     </row>
-    <row r="38" spans="1:89" ht="23.25" customHeight="1">
+    <row r="38" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>88</v>
       </c>
@@ -5294,7 +5298,7 @@
       <c r="CJ38" s="3"/>
       <c r="CK38" s="3"/>
     </row>
-    <row r="39" spans="1:89" ht="23.25" customHeight="1">
+    <row r="39" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>89</v>
       </c>
@@ -5395,7 +5399,7 @@
       <c r="CJ39" s="3"/>
       <c r="CK39" s="3"/>
     </row>
-    <row r="40" spans="1:89" ht="23.25" customHeight="1">
+    <row r="40" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>90</v>
       </c>
@@ -5496,7 +5500,7 @@
       <c r="CJ40" s="3"/>
       <c r="CK40" s="3"/>
     </row>
-    <row r="41" spans="1:89" ht="23.25" customHeight="1">
+    <row r="41" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>91</v>
       </c>
@@ -5597,7 +5601,7 @@
       <c r="CJ41" s="3"/>
       <c r="CK41" s="3"/>
     </row>
-    <row r="42" spans="1:89" ht="23.25" customHeight="1">
+    <row r="42" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>92</v>
       </c>
@@ -5698,7 +5702,7 @@
       <c r="CJ42" s="3"/>
       <c r="CK42" s="3"/>
     </row>
-    <row r="43" spans="1:89" ht="23.25" customHeight="1">
+    <row r="43" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>93</v>
       </c>
@@ -5799,7 +5803,7 @@
       <c r="CJ43" s="3"/>
       <c r="CK43" s="3"/>
     </row>
-    <row r="44" spans="1:89" ht="23.25" customHeight="1">
+    <row r="44" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>94</v>
       </c>
@@ -5900,7 +5904,7 @@
       <c r="CJ44" s="3"/>
       <c r="CK44" s="3"/>
     </row>
-    <row r="45" spans="1:89" ht="23.25" customHeight="1">
+    <row r="45" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>95</v>
       </c>
@@ -6001,7 +6005,7 @@
       <c r="CJ45" s="3"/>
       <c r="CK45" s="3"/>
     </row>
-    <row r="46" spans="1:89" ht="23.25" customHeight="1">
+    <row r="46" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>96</v>
       </c>
@@ -6102,7 +6106,7 @@
       <c r="CJ46" s="3"/>
       <c r="CK46" s="3"/>
     </row>
-    <row r="47" spans="1:89" ht="23.25" customHeight="1">
+    <row r="47" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>97</v>
       </c>
@@ -6203,7 +6207,7 @@
       <c r="CJ47" s="3"/>
       <c r="CK47" s="3"/>
     </row>
-    <row r="48" spans="1:89" ht="23.25" customHeight="1">
+    <row r="48" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>98</v>
       </c>
@@ -6304,7 +6308,7 @@
       <c r="CJ48" s="3"/>
       <c r="CK48" s="3"/>
     </row>
-    <row r="49" spans="1:89" ht="23.25" customHeight="1">
+    <row r="49" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>99</v>
       </c>
@@ -6405,7 +6409,7 @@
       <c r="CJ49" s="3"/>
       <c r="CK49" s="3"/>
     </row>
-    <row r="50" spans="1:89" ht="23.25" customHeight="1">
+    <row r="50" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>100</v>
       </c>
@@ -6506,7 +6510,7 @@
       <c r="CJ50" s="3"/>
       <c r="CK50" s="3"/>
     </row>
-    <row r="51" spans="1:89" ht="23.25" customHeight="1">
+    <row r="51" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>101</v>
       </c>
@@ -6607,7 +6611,7 @@
       <c r="CJ51" s="3"/>
       <c r="CK51" s="3"/>
     </row>
-    <row r="52" spans="1:89" ht="23.25" customHeight="1">
+    <row r="52" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>102</v>
       </c>
@@ -6708,7 +6712,7 @@
       <c r="CJ52" s="3"/>
       <c r="CK52" s="3"/>
     </row>
-    <row r="53" spans="1:89" ht="23.25" customHeight="1">
+    <row r="53" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>103</v>
       </c>
@@ -6809,7 +6813,7 @@
       <c r="CJ53" s="3"/>
       <c r="CK53" s="3"/>
     </row>
-    <row r="54" spans="1:89" ht="23.25" customHeight="1">
+    <row r="54" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>104</v>
       </c>
@@ -6910,7 +6914,7 @@
       <c r="CJ54" s="3"/>
       <c r="CK54" s="3"/>
     </row>
-    <row r="55" spans="1:89" ht="23.25" customHeight="1">
+    <row r="55" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>105</v>
       </c>
@@ -7011,7 +7015,7 @@
       <c r="CJ55" s="3"/>
       <c r="CK55" s="3"/>
     </row>
-    <row r="56" spans="1:89" ht="23.25" customHeight="1">
+    <row r="56" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>106</v>
       </c>
@@ -7112,7 +7116,7 @@
       <c r="CJ56" s="3"/>
       <c r="CK56" s="3"/>
     </row>
-    <row r="57" spans="1:89" ht="23.25" customHeight="1">
+    <row r="57" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>107</v>
       </c>
@@ -7213,7 +7217,7 @@
       <c r="CJ57" s="3"/>
       <c r="CK57" s="3"/>
     </row>
-    <row r="58" spans="1:89" ht="23.25" customHeight="1">
+    <row r="58" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>108</v>
       </c>
@@ -7314,7 +7318,7 @@
       <c r="CJ58" s="3"/>
       <c r="CK58" s="3"/>
     </row>
-    <row r="59" spans="1:89" ht="23.25" customHeight="1">
+    <row r="59" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>109</v>
       </c>
@@ -7415,7 +7419,7 @@
       <c r="CJ59" s="3"/>
       <c r="CK59" s="3"/>
     </row>
-    <row r="60" spans="1:89" ht="23.25" customHeight="1">
+    <row r="60" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>110</v>
       </c>
@@ -7516,7 +7520,7 @@
       <c r="CJ60" s="3"/>
       <c r="CK60" s="3"/>
     </row>
-    <row r="61" spans="1:89" ht="23.25" customHeight="1">
+    <row r="61" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>111</v>
       </c>
@@ -7617,7 +7621,7 @@
       <c r="CJ61" s="3"/>
       <c r="CK61" s="3"/>
     </row>
-    <row r="62" spans="1:89" ht="23.25" customHeight="1">
+    <row r="62" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>112</v>
       </c>
@@ -7718,7 +7722,7 @@
       <c r="CJ62" s="3"/>
       <c r="CK62" s="3"/>
     </row>
-    <row r="63" spans="1:89" ht="23.25" customHeight="1">
+    <row r="63" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>113</v>
       </c>
@@ -7819,7 +7823,7 @@
       <c r="CJ63" s="3"/>
       <c r="CK63" s="3"/>
     </row>
-    <row r="64" spans="1:89" ht="23.25" customHeight="1">
+    <row r="64" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>114</v>
       </c>
@@ -7920,7 +7924,7 @@
       <c r="CJ64" s="3"/>
       <c r="CK64" s="3"/>
     </row>
-    <row r="65" spans="1:89" ht="23.25" customHeight="1">
+    <row r="65" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>115</v>
       </c>
@@ -8021,7 +8025,7 @@
       <c r="CJ65" s="3"/>
       <c r="CK65" s="3"/>
     </row>
-    <row r="66" spans="1:89" ht="23.25" customHeight="1">
+    <row r="66" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>116</v>
       </c>
@@ -8122,7 +8126,7 @@
       <c r="CJ66" s="3"/>
       <c r="CK66" s="3"/>
     </row>
-    <row r="67" spans="1:89" ht="23.25" customHeight="1">
+    <row r="67" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>117</v>
       </c>
@@ -8223,7 +8227,7 @@
       <c r="CJ67" s="3"/>
       <c r="CK67" s="3"/>
     </row>
-    <row r="68" spans="1:89" ht="23.25" customHeight="1">
+    <row r="68" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>118</v>
       </c>
@@ -8324,7 +8328,7 @@
       <c r="CJ68" s="3"/>
       <c r="CK68" s="3"/>
     </row>
-    <row r="69" spans="1:89" ht="23.25" customHeight="1">
+    <row r="69" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>119</v>
       </c>
@@ -8425,7 +8429,7 @@
       <c r="CJ69" s="3"/>
       <c r="CK69" s="3"/>
     </row>
-    <row r="70" spans="1:89" ht="23.25" customHeight="1">
+    <row r="70" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>120</v>
       </c>
@@ -8526,7 +8530,7 @@
       <c r="CJ70" s="3"/>
       <c r="CK70" s="3"/>
     </row>
-    <row r="71" spans="1:89" ht="23.25" customHeight="1">
+    <row r="71" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>121</v>
       </c>
@@ -8627,7 +8631,7 @@
       <c r="CJ71" s="3"/>
       <c r="CK71" s="3"/>
     </row>
-    <row r="72" spans="1:89" ht="23.25" customHeight="1">
+    <row r="72" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>122</v>
       </c>
@@ -8728,7 +8732,7 @@
       <c r="CJ72" s="3"/>
       <c r="CK72" s="3"/>
     </row>
-    <row r="73" spans="1:89" ht="23.25" customHeight="1">
+    <row r="73" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>123</v>
       </c>
@@ -8829,7 +8833,7 @@
       <c r="CJ73" s="3"/>
       <c r="CK73" s="3"/>
     </row>
-    <row r="74" spans="1:89" ht="23.25" customHeight="1">
+    <row r="74" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>124</v>
       </c>
@@ -8930,7 +8934,7 @@
       <c r="CJ74" s="3"/>
       <c r="CK74" s="3"/>
     </row>
-    <row r="75" spans="1:89" ht="23.25" customHeight="1">
+    <row r="75" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>125</v>
       </c>
@@ -9031,7 +9035,7 @@
       <c r="CJ75" s="3"/>
       <c r="CK75" s="3"/>
     </row>
-    <row r="76" spans="1:89" ht="23.25" customHeight="1">
+    <row r="76" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>126</v>
       </c>
@@ -9132,7 +9136,7 @@
       <c r="CJ76" s="3"/>
       <c r="CK76" s="3"/>
     </row>
-    <row r="77" spans="1:89" ht="23.25" customHeight="1">
+    <row r="77" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>127</v>
       </c>
@@ -9233,7 +9237,7 @@
       <c r="CJ77" s="3"/>
       <c r="CK77" s="3"/>
     </row>
-    <row r="78" spans="1:89" ht="23.25" customHeight="1">
+    <row r="78" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>128</v>
       </c>
@@ -9334,7 +9338,7 @@
       <c r="CJ78" s="3"/>
       <c r="CK78" s="3"/>
     </row>
-    <row r="79" spans="1:89" ht="23.25" customHeight="1">
+    <row r="79" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>129</v>
       </c>
@@ -9435,7 +9439,7 @@
       <c r="CJ79" s="3"/>
       <c r="CK79" s="3"/>
     </row>
-    <row r="80" spans="1:89" ht="23.25" customHeight="1">
+    <row r="80" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>130</v>
       </c>
@@ -9536,7 +9540,7 @@
       <c r="CJ80" s="3"/>
       <c r="CK80" s="3"/>
     </row>
-    <row r="81" spans="1:89" ht="23.25" customHeight="1">
+    <row r="81" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>131</v>
       </c>
@@ -9637,7 +9641,7 @@
       <c r="CJ81" s="3"/>
       <c r="CK81" s="3"/>
     </row>
-    <row r="82" spans="1:89" ht="23.25" customHeight="1">
+    <row r="82" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>132</v>
       </c>
@@ -9738,7 +9742,7 @@
       <c r="CJ82" s="3"/>
       <c r="CK82" s="3"/>
     </row>
-    <row r="83" spans="1:89" ht="23.25" customHeight="1">
+    <row r="83" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>133</v>
       </c>
@@ -9839,7 +9843,7 @@
       <c r="CJ83" s="3"/>
       <c r="CK83" s="3"/>
     </row>
-    <row r="84" spans="1:89" ht="23.25" customHeight="1">
+    <row r="84" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>134</v>
       </c>
@@ -9940,7 +9944,7 @@
       <c r="CJ84" s="3"/>
       <c r="CK84" s="3"/>
     </row>
-    <row r="85" spans="1:89" ht="23.25" customHeight="1">
+    <row r="85" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>135</v>
       </c>
@@ -10041,7 +10045,7 @@
       <c r="CJ85" s="3"/>
       <c r="CK85" s="3"/>
     </row>
-    <row r="86" spans="1:89" ht="23.25" customHeight="1">
+    <row r="86" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>136</v>
       </c>
@@ -10142,7 +10146,7 @@
       <c r="CJ86" s="3"/>
       <c r="CK86" s="3"/>
     </row>
-    <row r="87" spans="1:89" ht="23.25" customHeight="1">
+    <row r="87" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>137</v>
       </c>
@@ -10243,7 +10247,7 @@
       <c r="CJ87" s="3"/>
       <c r="CK87" s="3"/>
     </row>
-    <row r="88" spans="1:89" ht="23.25" customHeight="1">
+    <row r="88" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>138</v>
       </c>
@@ -10344,7 +10348,7 @@
       <c r="CJ88" s="3"/>
       <c r="CK88" s="3"/>
     </row>
-    <row r="89" spans="1:89" ht="23.25" customHeight="1">
+    <row r="89" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>139</v>
       </c>
@@ -10445,7 +10449,7 @@
       <c r="CJ89" s="3"/>
       <c r="CK89" s="3"/>
     </row>
-    <row r="90" spans="1:89" ht="23.25" customHeight="1">
+    <row r="90" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>140</v>
       </c>
@@ -10546,7 +10550,7 @@
       <c r="CJ90" s="3"/>
       <c r="CK90" s="3"/>
     </row>
-    <row r="91" spans="1:89" ht="23.25" customHeight="1">
+    <row r="91" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>141</v>
       </c>
@@ -10647,7 +10651,7 @@
       <c r="CJ91" s="3"/>
       <c r="CK91" s="3"/>
     </row>
-    <row r="92" spans="1:89" ht="23.25" customHeight="1">
+    <row r="92" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>142</v>
       </c>
@@ -10748,7 +10752,7 @@
       <c r="CJ92" s="3"/>
       <c r="CK92" s="3"/>
     </row>
-    <row r="93" spans="1:89" ht="23.25" customHeight="1">
+    <row r="93" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>143</v>
       </c>
@@ -10849,7 +10853,7 @@
       <c r="CJ93" s="3"/>
       <c r="CK93" s="3"/>
     </row>
-    <row r="94" spans="1:89" ht="23.25" customHeight="1">
+    <row r="94" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>144</v>
       </c>
@@ -10950,7 +10954,7 @@
       <c r="CJ94" s="3"/>
       <c r="CK94" s="3"/>
     </row>
-    <row r="95" spans="1:89" ht="23.25" customHeight="1">
+    <row r="95" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>145</v>
       </c>
@@ -11051,7 +11055,7 @@
       <c r="CJ95" s="3"/>
       <c r="CK95" s="3"/>
     </row>
-    <row r="96" spans="1:89" ht="23.25" customHeight="1">
+    <row r="96" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>146</v>
       </c>
@@ -11152,7 +11156,7 @@
       <c r="CJ96" s="3"/>
       <c r="CK96" s="3"/>
     </row>
-    <row r="97" spans="1:89" ht="23.25" customHeight="1">
+    <row r="97" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>147</v>
       </c>
@@ -11253,7 +11257,7 @@
       <c r="CJ97" s="3"/>
       <c r="CK97" s="3"/>
     </row>
-    <row r="98" spans="1:89" ht="23.25" customHeight="1">
+    <row r="98" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>148</v>
       </c>
@@ -11354,7 +11358,7 @@
       <c r="CJ98" s="3"/>
       <c r="CK98" s="3"/>
     </row>
-    <row r="99" spans="1:89" ht="23.25" customHeight="1">
+    <row r="99" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>149</v>
       </c>
@@ -11455,7 +11459,7 @@
       <c r="CJ99" s="3"/>
       <c r="CK99" s="3"/>
     </row>
-    <row r="100" spans="1:89" ht="23.25" customHeight="1">
+    <row r="100" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>150</v>
       </c>
@@ -11556,7 +11560,7 @@
       <c r="CJ100" s="3"/>
       <c r="CK100" s="3"/>
     </row>
-    <row r="101" spans="1:89" ht="23.25" customHeight="1">
+    <row r="101" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>151</v>
       </c>
@@ -11657,7 +11661,7 @@
       <c r="CJ101" s="3"/>
       <c r="CK101" s="3"/>
     </row>
-    <row r="102" spans="1:89" ht="23.25" customHeight="1">
+    <row r="102" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>152</v>
       </c>
@@ -11758,7 +11762,7 @@
       <c r="CJ102" s="3"/>
       <c r="CK102" s="3"/>
     </row>
-    <row r="103" spans="1:89" ht="23.25" customHeight="1">
+    <row r="103" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>153</v>
       </c>
@@ -11859,7 +11863,7 @@
       <c r="CJ103" s="3"/>
       <c r="CK103" s="3"/>
     </row>
-    <row r="104" spans="1:89" ht="23.25" customHeight="1">
+    <row r="104" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>154</v>
       </c>
@@ -11960,7 +11964,7 @@
       <c r="CJ104" s="3"/>
       <c r="CK104" s="3"/>
     </row>
-    <row r="105" spans="1:89" ht="23.25" customHeight="1">
+    <row r="105" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>155</v>
       </c>
@@ -12061,7 +12065,7 @@
       <c r="CJ105" s="3"/>
       <c r="CK105" s="3"/>
     </row>
-    <row r="106" spans="1:89" ht="23.25" customHeight="1">
+    <row r="106" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>156</v>
       </c>
@@ -12162,7 +12166,7 @@
       <c r="CJ106" s="3"/>
       <c r="CK106" s="3"/>
     </row>
-    <row r="107" spans="1:89" ht="23.25" customHeight="1">
+    <row r="107" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>157</v>
       </c>
@@ -12263,7 +12267,7 @@
       <c r="CJ107" s="3"/>
       <c r="CK107" s="3"/>
     </row>
-    <row r="108" spans="1:89" ht="23.25" customHeight="1">
+    <row r="108" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>158</v>
       </c>
@@ -12364,7 +12368,7 @@
       <c r="CJ108" s="3"/>
       <c r="CK108" s="3"/>
     </row>
-    <row r="109" spans="1:89" ht="23.25" customHeight="1">
+    <row r="109" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>159</v>
       </c>
@@ -12465,7 +12469,7 @@
       <c r="CJ109" s="3"/>
       <c r="CK109" s="3"/>
     </row>
-    <row r="110" spans="1:89" ht="23.25" customHeight="1">
+    <row r="110" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>160</v>
       </c>
@@ -12566,7 +12570,7 @@
       <c r="CJ110" s="3"/>
       <c r="CK110" s="3"/>
     </row>
-    <row r="111" spans="1:89" ht="23.25" customHeight="1">
+    <row r="111" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>161</v>
       </c>
@@ -12667,7 +12671,7 @@
       <c r="CJ111" s="3"/>
       <c r="CK111" s="3"/>
     </row>
-    <row r="112" spans="1:89" ht="23.25" customHeight="1">
+    <row r="112" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>162</v>
       </c>
@@ -12768,7 +12772,7 @@
       <c r="CJ112" s="3"/>
       <c r="CK112" s="3"/>
     </row>
-    <row r="113" spans="1:89" ht="23.25" customHeight="1">
+    <row r="113" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>163</v>
       </c>
@@ -12869,7 +12873,7 @@
       <c r="CJ113" s="3"/>
       <c r="CK113" s="3"/>
     </row>
-    <row r="114" spans="1:89" ht="23.25" customHeight="1">
+    <row r="114" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>164</v>
       </c>
@@ -12970,7 +12974,7 @@
       <c r="CJ114" s="3"/>
       <c r="CK114" s="3"/>
     </row>
-    <row r="115" spans="1:89" ht="23.25" customHeight="1">
+    <row r="115" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>165</v>
       </c>
@@ -13071,7 +13075,7 @@
       <c r="CJ115" s="3"/>
       <c r="CK115" s="3"/>
     </row>
-    <row r="116" spans="1:89" ht="23.25" customHeight="1">
+    <row r="116" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>166</v>
       </c>
@@ -13172,7 +13176,7 @@
       <c r="CJ116" s="3"/>
       <c r="CK116" s="3"/>
     </row>
-    <row r="117" spans="1:89" ht="23.25" customHeight="1">
+    <row r="117" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>167</v>
       </c>
@@ -13273,7 +13277,7 @@
       <c r="CJ117" s="3"/>
       <c r="CK117" s="3"/>
     </row>
-    <row r="118" spans="1:89" ht="23.25" customHeight="1">
+    <row r="118" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>168</v>
       </c>
@@ -13374,7 +13378,7 @@
       <c r="CJ118" s="3"/>
       <c r="CK118" s="3"/>
     </row>
-    <row r="119" spans="1:89" ht="23.25" customHeight="1">
+    <row r="119" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>169</v>
       </c>
@@ -13475,21 +13479,21 @@
       <c r="CJ119" s="3"/>
       <c r="CK119" s="3"/>
     </row>
-    <row r="120" spans="1:89" ht="23.25" customHeight="1">
+    <row r="120" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>170</v>
       </c>
       <c r="B120" s="3">
-        <v>100.7</v>
+        <v>0</v>
       </c>
       <c r="C120" s="3">
         <v>0</v>
       </c>
       <c r="D120" s="3">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="E120" s="3">
-        <v>99.9</v>
+        <v>0</v>
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
@@ -13576,21 +13580,21 @@
       <c r="CJ120" s="3"/>
       <c r="CK120" s="3"/>
     </row>
-    <row r="121" spans="1:89" ht="23.25" customHeight="1">
+    <row r="121" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>171</v>
       </c>
       <c r="B121" s="3">
-        <v>98.4</v>
+        <v>0</v>
       </c>
       <c r="C121" s="3">
-        <v>-2.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="D121" s="3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E121" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
@@ -13677,21 +13681,21 @@
       <c r="CJ121" s="3"/>
       <c r="CK121" s="3"/>
     </row>
-    <row r="122" spans="1:89" ht="23.25" customHeight="1">
+    <row r="122" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B122" s="3">
-        <v>100.9</v>
+        <v>0</v>
       </c>
       <c r="C122" s="3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D122" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E122" s="3">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
@@ -13778,21 +13782,21 @@
       <c r="CJ122" s="3"/>
       <c r="CK122" s="3"/>
     </row>
-    <row r="123" spans="1:89" ht="23.25" customHeight="1">
+    <row r="123" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B123" s="3">
-        <v>103.7</v>
+        <v>0</v>
       </c>
       <c r="C123" s="3">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="D123" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E123" s="3">
-        <v>101.8</v>
+        <v>0</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
@@ -13879,21 +13883,21 @@
       <c r="CJ123" s="3"/>
       <c r="CK123" s="3"/>
     </row>
-    <row r="124" spans="1:89" ht="23.25" customHeight="1">
+    <row r="124" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>174</v>
       </c>
       <c r="B124" s="3">
-        <v>100.8</v>
+        <v>0</v>
       </c>
       <c r="C124" s="3">
-        <v>-2.9</v>
+        <v>0</v>
       </c>
       <c r="D124" s="3">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="E124" s="3">
-        <v>101.5</v>
+        <v>0</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
@@ -13980,21 +13984,21 @@
       <c r="CJ124" s="3"/>
       <c r="CK124" s="3"/>
     </row>
-    <row r="125" spans="1:89" ht="23.25" customHeight="1">
+    <row r="125" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>175</v>
       </c>
       <c r="B125" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C125" s="3">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="D125" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E125" s="3">
-        <v>100.9</v>
+        <v>0</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3"/>
@@ -14081,21 +14085,21 @@
       <c r="CJ125" s="3"/>
       <c r="CK125" s="3"/>
     </row>
-    <row r="126" spans="1:89" ht="23.25" customHeight="1">
+    <row r="126" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>176</v>
       </c>
       <c r="B126" s="3">
-        <v>101.8</v>
+        <v>0</v>
       </c>
       <c r="C126" s="3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D126" s="3">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="E126" s="3">
-        <v>100.8</v>
+        <v>0</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
@@ -14182,21 +14186,21 @@
       <c r="CJ126" s="3"/>
       <c r="CK126" s="3"/>
     </row>
-    <row r="127" spans="1:89" ht="23.25" customHeight="1">
+    <row r="127" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>177</v>
       </c>
       <c r="B127" s="3">
-        <v>100.7</v>
+        <v>0</v>
       </c>
       <c r="C127" s="3">
-        <v>-1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="D127" s="3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="E127" s="3">
-        <v>96.9</v>
+        <v>0</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
@@ -14283,21 +14287,21 @@
       <c r="CJ127" s="3"/>
       <c r="CK127" s="3"/>
     </row>
-    <row r="128" spans="1:89" ht="23.25" customHeight="1">
+    <row r="128" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>178</v>
       </c>
       <c r="B128" s="3">
-        <v>88.2</v>
+        <v>0</v>
       </c>
       <c r="C128" s="3">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="D128" s="3">
-        <v>-11.5</v>
+        <v>0</v>
       </c>
       <c r="E128" s="3">
-        <v>93.4</v>
+        <v>0</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="3"/>
@@ -14384,21 +14388,21 @@
       <c r="CJ128" s="3"/>
       <c r="CK128" s="3"/>
     </row>
-    <row r="129" spans="1:89" ht="23.25" customHeight="1">
+    <row r="129" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>179</v>
       </c>
       <c r="B129" s="3">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="C129" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D129" s="3">
-        <v>-10.4</v>
+        <v>0</v>
       </c>
       <c r="E129" s="3">
-        <v>91.5</v>
+        <v>0</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
@@ -14485,21 +14489,21 @@
       <c r="CJ129" s="3"/>
       <c r="CK129" s="3"/>
     </row>
-    <row r="130" spans="1:89" ht="23.25" customHeight="1">
+    <row r="130" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>180</v>
       </c>
       <c r="B130" s="3">
-        <v>95.2</v>
+        <v>0</v>
       </c>
       <c r="C130" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D130" s="3">
-        <v>-6.7</v>
+        <v>0</v>
       </c>
       <c r="E130" s="3">
-        <v>93.3</v>
+        <v>0</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
@@ -14586,21 +14590,21 @@
       <c r="CJ130" s="3"/>
       <c r="CK130" s="3"/>
     </row>
-    <row r="131" spans="1:89" ht="23.25" customHeight="1">
+    <row r="131" spans="1:89" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>181</v>
       </c>
       <c r="B131" s="3">
-        <v>93.4</v>
+        <v>0</v>
       </c>
       <c r="C131" s="3">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="D131" s="3">
-        <v>-7.3</v>
+        <v>0</v>
       </c>
       <c r="E131" s="3">
-        <v>94.3</v>
+        <v>0</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
@@ -14689,16 +14693,27 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="BR5:BU5"/>
-    <mergeCell ref="BV5:BY5"/>
-    <mergeCell ref="BZ5:CC5"/>
-    <mergeCell ref="CD5:CG5"/>
-    <mergeCell ref="CH5:CK5"/>
-    <mergeCell ref="AX5:BA5"/>
-    <mergeCell ref="BB5:BE5"/>
-    <mergeCell ref="BF5:BI5"/>
-    <mergeCell ref="BJ5:BM5"/>
-    <mergeCell ref="BN5:BQ5"/>
+    <mergeCell ref="B1:CK1"/>
+    <mergeCell ref="B2:CK2"/>
+    <mergeCell ref="B3:CK3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="AH4:AK4"/>
+    <mergeCell ref="AL4:AO4"/>
+    <mergeCell ref="AP4:AS4"/>
+    <mergeCell ref="AT4:AW4"/>
+    <mergeCell ref="AX4:BA4"/>
+    <mergeCell ref="BB4:BE4"/>
+    <mergeCell ref="BF4:BI4"/>
+    <mergeCell ref="BJ4:BM4"/>
+    <mergeCell ref="BN4:BQ4"/>
+    <mergeCell ref="BR4:BU4"/>
     <mergeCell ref="BV4:BY4"/>
     <mergeCell ref="BZ4:CC4"/>
     <mergeCell ref="CD4:CG4"/>
@@ -14715,27 +14730,16 @@
     <mergeCell ref="AL5:AO5"/>
     <mergeCell ref="AP5:AS5"/>
     <mergeCell ref="AT5:AW5"/>
-    <mergeCell ref="BB4:BE4"/>
-    <mergeCell ref="BF4:BI4"/>
-    <mergeCell ref="BJ4:BM4"/>
-    <mergeCell ref="BN4:BQ4"/>
-    <mergeCell ref="BR4:BU4"/>
-    <mergeCell ref="B1:CK1"/>
-    <mergeCell ref="B2:CK2"/>
-    <mergeCell ref="B3:CK3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="AH4:AK4"/>
-    <mergeCell ref="AL4:AO4"/>
-    <mergeCell ref="AP4:AS4"/>
-    <mergeCell ref="AT4:AW4"/>
-    <mergeCell ref="AX4:BA4"/>
+    <mergeCell ref="AX5:BA5"/>
+    <mergeCell ref="BB5:BE5"/>
+    <mergeCell ref="BF5:BI5"/>
+    <mergeCell ref="BJ5:BM5"/>
+    <mergeCell ref="BN5:BQ5"/>
+    <mergeCell ref="BR5:BU5"/>
+    <mergeCell ref="BV5:BY5"/>
+    <mergeCell ref="BZ5:CC5"/>
+    <mergeCell ref="CD5:CG5"/>
+    <mergeCell ref="CH5:CK5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14745,84 +14749,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="148"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.25" customHeight="1">
+    <row r="1" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="23.25" customHeight="1">
+    <row r="2" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="23.25" customHeight="1">
+    <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="23.25" customHeight="1">
+    <row r="4" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+    <row r="5" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:1" ht="23.25" customHeight="1">
+    <row r="6" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:1" ht="23.25" customHeight="1">
+    <row r="7" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="23.25" customHeight="1">
+    <row r="8" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="23.25" customHeight="1">
+    <row r="9" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="23.25" customHeight="1">
+    <row r="10" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="23.25" customHeight="1">
+    <row r="11" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:1" ht="23.25" customHeight="1">
+    <row r="12" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="23.25" customHeight="1">
+    <row r="13" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:1" ht="23.25" customHeight="1">
+    <row r="14" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="23.25" customHeight="1">
+    <row r="15" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="23.25" customHeight="1">
+    <row r="16" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="23.25" customHeight="1">
+    <row r="17" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>193</v>
       </c>
